--- a/Week12/Day2/Ex_XP/List of Holidays.xlsx
+++ b/Week12/Day2/Ex_XP/List of Holidays.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AurianeB/DI-Bootcamp/Week12/Day2/Ex_XP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D08F872-8C96-C54D-A644-B810A4871FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9500D5-488D-104C-A87F-5FB0EC754F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="660" windowWidth="28660" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="660" windowWidth="28660" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId4"/>
+    <pivotCache cacheId="34" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -384,23 +384,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Auriane Bouaziz" refreshedDate="46288.840624999997" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{9E986716-8DA2-F249-B84E-D6DB4D4BDCAA}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Auriane Bouaziz" refreshedDate="46289.576475462964" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{9E986716-8DA2-F249-B84E-D6DB4D4BDCAA}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:F31" sheet="Source Data"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Country" numFmtId="0">
-      <sharedItems count="9">
-        <s v="Australia"/>
-        <s v="Chile"/>
-        <s v="England"/>
-        <s v="France"/>
-        <s v="Germany"/>
-        <s v="Peru"/>
-        <s v="Saudi Arabia"/>
-        <s v="Spain"/>
-        <s v="Trinidad"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Resort Name" numFmtId="0">
       <sharedItems count="21">
@@ -455,7 +445,7 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
   <r>
-    <x v="0"/>
+    <s v="Australia"/>
     <x v="0"/>
     <n v="32"/>
     <x v="0"/>
@@ -463,7 +453,7 @@
     <s v="I990AUS"/>
   </r>
   <r>
-    <x v="0"/>
+    <s v="Australia"/>
     <x v="1"/>
     <n v="28"/>
     <x v="0"/>
@@ -471,7 +461,7 @@
     <s v="AUS112J"/>
   </r>
   <r>
-    <x v="1"/>
+    <s v="Chile"/>
     <x v="2"/>
     <n v="21"/>
     <x v="0"/>
@@ -479,7 +469,7 @@
     <s v="CH266H"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="England"/>
     <x v="3"/>
     <n v="3"/>
     <x v="1"/>
@@ -487,7 +477,7 @@
     <s v="I456UK"/>
   </r>
   <r>
-    <x v="2"/>
+    <s v="England"/>
     <x v="4"/>
     <n v="1"/>
     <x v="2"/>
@@ -495,7 +485,7 @@
     <s v="BG726H"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="5"/>
     <n v="14"/>
     <x v="0"/>
@@ -503,7 +493,7 @@
     <s v="A7995FR"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="6"/>
     <n v="5"/>
     <x v="1"/>
@@ -511,7 +501,7 @@
     <s v="TH789FR"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="6"/>
     <n v="3"/>
     <x v="1"/>
@@ -519,7 +509,7 @@
     <s v="TH788FR"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="7"/>
     <n v="7"/>
     <x v="0"/>
@@ -527,7 +517,7 @@
     <s v="I7897FR"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="8"/>
     <n v="7"/>
     <x v="1"/>
@@ -535,7 +525,7 @@
     <s v="SG7637L"/>
   </r>
   <r>
-    <x v="3"/>
+    <s v="France"/>
     <x v="9"/>
     <n v="7"/>
     <x v="0"/>
@@ -543,7 +533,7 @@
     <s v="FR5625J"/>
   </r>
   <r>
-    <x v="4"/>
+    <s v="Germany"/>
     <x v="10"/>
     <n v="4"/>
     <x v="2"/>
@@ -551,7 +541,7 @@
     <s v="A111G"/>
   </r>
   <r>
-    <x v="4"/>
+    <s v="Germany"/>
     <x v="11"/>
     <n v="7"/>
     <x v="2"/>
@@ -559,7 +549,7 @@
     <s v="BR6736G"/>
   </r>
   <r>
-    <x v="5"/>
+    <s v="Peru"/>
     <x v="12"/>
     <n v="21"/>
     <x v="0"/>
@@ -567,7 +557,7 @@
     <s v="PG7836G"/>
   </r>
   <r>
-    <x v="6"/>
+    <s v="Saudi Arabia"/>
     <x v="13"/>
     <n v="14"/>
     <x v="0"/>
@@ -575,7 +565,7 @@
     <s v="KSA8987"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="14"/>
     <n v="4"/>
     <x v="1"/>
@@ -583,7 +573,7 @@
     <s v="I6675SP"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="15"/>
     <n v="6"/>
     <x v="0"/>
@@ -591,7 +581,7 @@
     <s v="TH990ESP"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="16"/>
     <n v="16"/>
     <x v="0"/>
@@ -599,7 +589,7 @@
     <s v="A776ESP"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="17"/>
     <n v="14"/>
     <x v="0"/>
@@ -607,7 +597,7 @@
     <s v="NM9876Y"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="17"/>
     <n v="10"/>
     <x v="0"/>
@@ -615,7 +605,7 @@
     <s v="TH8956SP"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="14"/>
     <n v="8"/>
     <x v="0"/>
@@ -623,7 +613,7 @@
     <s v="AJ9836L"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="14"/>
     <n v="7"/>
     <x v="2"/>
@@ -631,7 +621,7 @@
     <s v="GG9836P"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="16"/>
     <n v="14"/>
     <x v="0"/>
@@ -639,7 +629,7 @@
     <s v="PL8726P"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="14"/>
     <n v="4"/>
     <x v="1"/>
@@ -647,7 +637,7 @@
     <s v="I6675SP"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="17"/>
     <n v="14"/>
     <x v="1"/>
@@ -655,7 +645,7 @@
     <s v="SV767HH"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="18"/>
     <n v="8"/>
     <x v="0"/>
@@ -663,7 +653,7 @@
     <s v="WE6735L"/>
   </r>
   <r>
-    <x v="7"/>
+    <s v="Spain"/>
     <x v="19"/>
     <n v="10"/>
     <x v="0"/>
@@ -671,7 +661,7 @@
     <s v="GR7878G"/>
   </r>
   <r>
-    <x v="8"/>
+    <s v="Trinidad"/>
     <x v="20"/>
     <n v="14"/>
     <x v="0"/>
@@ -682,23 +672,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1AC6AA98-C825-B04E-AFE5-B672719C9080}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1AC6AA98-C825-B04E-AFE5-B672719C9080}" name="PivotTable1" cacheId="34" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="22">
         <item x="14"/>
